--- a/B_Data/Raw_data/Bank_capital/Assets_pre_2002.xlsx
+++ b/B_Data/Raw_data/Bank_capital/Assets_pre_2002.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="27">
   <si>
     <t>Date</t>
   </si>
@@ -52,12 +52,6 @@
   </si>
   <si>
     <t>Table4</t>
-  </si>
-  <si>
-    <t>All raw data is located</t>
-  </si>
-  <si>
-    <t>House_credit_cycles\B_Data\Raw_data\Bank_capital\Raw_data\CBI_STATS</t>
   </si>
   <si>
     <r>
@@ -185,6 +179,9 @@
   </si>
   <si>
     <t>I extrapolated the domestic assets provided by domestic credit institutions with OLS regression, see R code C_Properties/C1.Bank_crisis.R, to get data from 1970s</t>
+  </si>
+  <si>
+    <t>Sources:</t>
   </si>
 </sst>
 </file>
@@ -2269,7 +2266,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="B2:S25"/>
+  <dimension ref="B2:S24"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.54296875" customWidth="1"/>
@@ -2278,7 +2275,7 @@
   <sheetData>
     <row r="2" spans="2:19" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="24" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
@@ -2300,7 +2297,7 @@
     </row>
     <row r="3" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B3" s="8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -2322,7 +2319,7 @@
     </row>
     <row r="4" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B4" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -2364,7 +2361,7 @@
     </row>
     <row r="6" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B6" s="15" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
@@ -2384,42 +2381,42 @@
       <c r="R6" s="3"/>
       <c r="S6" s="9"/>
     </row>
-    <row r="7" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:19" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B7" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="3"/>
-      <c r="P7" s="3"/>
-      <c r="Q7" s="3"/>
-      <c r="R7" s="3"/>
-      <c r="S7" s="9"/>
-    </row>
-    <row r="8" spans="2:19" s="3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="8" t="s">
-        <v>18</v>
-      </c>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B8" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+      <c r="P8" s="3"/>
+      <c r="Q8" s="3"/>
+      <c r="R8" s="3"/>
+      <c r="S8" s="9"/>
     </row>
     <row r="9" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B9" s="22" t="s">
-        <v>21</v>
+      <c r="B9" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
@@ -2433,8 +2430,8 @@
       <c r="S9" s="9"/>
     </row>
     <row r="10" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B10" s="8" t="s">
-        <v>19</v>
+      <c r="B10" s="23" t="s">
+        <v>18</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
@@ -2452,12 +2449,10 @@
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
-      <c r="S10" s="9"/>
+      <c r="S10" s="3"/>
     </row>
     <row r="11" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B11" s="23" t="s">
-        <v>20</v>
-      </c>
+      <c r="B11" s="8"/>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -2477,7 +2472,9 @@
       <c r="S11" s="3"/>
     </row>
     <row r="12" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B12" s="8"/>
+      <c r="B12" s="15" t="s">
+        <v>12</v>
+      </c>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -2497,8 +2494,8 @@
       <c r="S12" s="3"/>
     </row>
     <row r="13" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B13" s="15" t="s">
-        <v>14</v>
+      <c r="B13" s="8" t="s">
+        <v>13</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
@@ -2518,36 +2515,36 @@
       <c r="R13" s="3"/>
       <c r="S13" s="3"/>
     </row>
-    <row r="14" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:19" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B14" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="3"/>
-      <c r="P14" s="3"/>
-      <c r="Q14" s="3"/>
-      <c r="R14" s="3"/>
-      <c r="S14" s="3"/>
-    </row>
-    <row r="15" spans="2:19" s="3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="8" t="s">
-        <v>16</v>
-      </c>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B15" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3"/>
+      <c r="O15" s="3"/>
+      <c r="P15" s="3"/>
+      <c r="Q15" s="3"/>
+      <c r="R15" s="3"/>
+      <c r="S15" s="9"/>
     </row>
     <row r="16" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B16" s="10" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -2569,7 +2566,7 @@
     </row>
     <row r="17" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B17" s="10" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
@@ -2590,8 +2587,8 @@
       <c r="S17" s="9"/>
     </row>
     <row r="18" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B18" s="10" t="s">
-        <v>6</v>
+      <c r="B18" s="8" t="s">
+        <v>20</v>
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
@@ -2613,7 +2610,7 @@
     </row>
     <row r="19" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B19" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
@@ -2635,7 +2632,7 @@
     </row>
     <row r="20" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B20" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
@@ -2656,9 +2653,7 @@
       <c r="S20" s="9"/>
     </row>
     <row r="21" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B21" s="8" t="s">
-        <v>24</v>
-      </c>
+      <c r="B21" s="15"/>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
@@ -2678,7 +2673,9 @@
       <c r="S21" s="9"/>
     </row>
     <row r="22" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B22" s="15"/>
+      <c r="B22" s="11" t="s">
+        <v>7</v>
+      </c>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
@@ -2698,9 +2695,7 @@
       <c r="S22" s="9"/>
     </row>
     <row r="23" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B23" s="11" t="s">
-        <v>7</v>
-      </c>
+      <c r="B23" s="8"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
@@ -2719,45 +2714,25 @@
       <c r="R23" s="3"/>
       <c r="S23" s="9"/>
     </row>
-    <row r="24" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B24" s="8"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
-      <c r="M24" s="3"/>
-      <c r="N24" s="3"/>
-      <c r="O24" s="3"/>
-      <c r="P24" s="3"/>
-      <c r="Q24" s="3"/>
-      <c r="R24" s="3"/>
-      <c r="S24" s="9"/>
-    </row>
-    <row r="25" spans="2:19" ht="8" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="12"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="H25" s="5"/>
-      <c r="I25" s="5"/>
-      <c r="J25" s="5"/>
-      <c r="K25" s="5"/>
-      <c r="L25" s="5"/>
-      <c r="M25" s="5"/>
-      <c r="N25" s="5"/>
-      <c r="O25" s="5"/>
-      <c r="P25" s="5"/>
-      <c r="Q25" s="5"/>
-      <c r="R25" s="5"/>
-      <c r="S25" s="13"/>
+    <row r="24" spans="2:19" ht="8" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B24" s="12"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="5"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="5"/>
+      <c r="N24" s="5"/>
+      <c r="O24" s="5"/>
+      <c r="P24" s="5"/>
+      <c r="Q24" s="5"/>
+      <c r="R24" s="5"/>
+      <c r="S24" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2792,7 +2767,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="20" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
@@ -2810,7 +2785,7 @@
         <v>276486</v>
       </c>
       <c r="F2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -6812,7 +6787,7 @@
         <v>3</v>
       </c>
       <c r="G1" s="20" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
@@ -11267,7 +11242,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A39F95C3-5EEC-4065-B741-1F2582C36990}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8ECB7C15-F0B5-4865-8C6D-9B0D0A55525A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
